--- a/resouces/target/择校.xlsx
+++ b/resouces/target/择校.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\documents\MyPGEE\resouces\target\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4C812E-A72B-44FE-99B2-FAB4201D13A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17905A40-7A52-45E3-896F-13FB5CB68C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5FE05B2F-D04D-4FA0-9C85-447D9885FCB9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,35 @@
   </si>
   <si>
     <t>10-12-x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都理工大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(00)不区分研究方向</t>
+  </si>
+  <si>
+    <t>北京交通大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大连海事大学</t>
+  </si>
+  <si>
+    <t>301/34/51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(01)软件方法与技术</t>
+  </si>
+  <si>
+    <t>302/34/51</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF2560D-83C2-445E-BF1D-8111E8F06802}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.3984375" style="2" customWidth="1"/>
@@ -522,10 +551,58 @@
         <v>12</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>22861</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 B2:B1048576" xr:uid="{227C74D3-38D2-4212-958E-709D693C5335}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{227C74D3-38D2-4212-958E-709D693C5335}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
